--- a/test_data_enhanced.xlsx
+++ b/test_data_enhanced.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15840" activeTab="4"/>
+    <workbookView windowHeight="15920"/>
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="93">
   <si>
     <t>模块编号</t>
   </si>
@@ -57,6 +57,9 @@
     <t>追踪关系</t>
   </si>
   <si>
+    <t>test</t>
+  </si>
+  <si>
     <t>登录功能</t>
   </si>
   <si>
@@ -280,9 +283,6 @@
   </si>
   <si>
     <t>v1.0</t>
-  </si>
-  <si>
-    <t>test</t>
   </si>
   <si>
     <t>test2</t>
@@ -322,14 +322,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -785,148 +778,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1278,10 +1271,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="7"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1306,161 +1299,167 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>5.2</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>15</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>5.2</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>5.3</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>5.5</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>5.5</v>
       </c>
       <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>5.5</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1477,101 +1476,101 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1588,70 +1587,70 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1668,41 +1667,41 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1714,12 +1713,12 @@
         <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1731,12 +1730,12 @@
         <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1748,7 +1747,7 @@
         <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1765,13 +1764,13 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s">
         <v>90</v>
@@ -1780,7 +1779,7 @@
         <v>91</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1791,16 +1790,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1820,7 +1819,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1840,7 +1839,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1860,7 +1859,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
